--- a/results/excel_reports/independent_resnet50_black.xlsx
+++ b/results/excel_reports/independent_resnet50_black.xlsx
@@ -401,6 +401,38 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'Top-1 Accuracy'!A9</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Top-1 Accuracy'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Top-1 Accuracy'!$B$9:$V$9</f>
+            </numRef>
+          </val>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -722,6 +754,38 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'Top-5 Accuracy'!A9</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Top-5 Accuracy'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Top-5 Accuracy'!$B$9:$V$9</f>
+            </numRef>
+          </val>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -795,7 +859,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>11</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -822,7 +886,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>11</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -1132,11 +1196,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
@@ -1232,68 +1296,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>u2net</t>
+          <t>dino+u2net_sum</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.92</v>
+        <v>0.9199199199199199</v>
       </c>
       <c r="C2" t="n">
-        <v>0.916</v>
+        <v>0.896</v>
       </c>
       <c r="D2" t="n">
-        <v>0.916</v>
+        <v>0.889</v>
       </c>
       <c r="E2" t="n">
-        <v>0.913</v>
+        <v>0.876</v>
       </c>
       <c r="F2" t="n">
-        <v>0.907</v>
+        <v>0.863</v>
       </c>
       <c r="G2" t="n">
-        <v>0.899</v>
+        <v>0.843</v>
       </c>
       <c r="H2" t="n">
-        <v>0.902</v>
+        <v>0.83</v>
       </c>
       <c r="I2" t="n">
-        <v>0.897</v>
+        <v>0.82</v>
       </c>
       <c r="J2" t="n">
-        <v>0.892</v>
+        <v>0.801</v>
       </c>
       <c r="K2" t="n">
-        <v>0.878</v>
+        <v>0.76</v>
       </c>
       <c r="L2" t="n">
-        <v>0.861</v>
+        <v>0.734</v>
       </c>
       <c r="M2" t="n">
-        <v>0.843</v>
+        <v>0.694</v>
       </c>
       <c r="N2" t="n">
-        <v>0.828</v>
+        <v>0.647</v>
       </c>
       <c r="O2" t="n">
-        <v>0.786</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>0.76</v>
+        <v>0.49</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.712</v>
+        <v>0.401</v>
       </c>
       <c r="R2" t="n">
-        <v>0.633</v>
+        <v>0.308</v>
       </c>
       <c r="S2" t="n">
-        <v>0.533</v>
+        <v>0.222</v>
       </c>
       <c r="T2" t="n">
-        <v>0.366</v>
+        <v>0.117</v>
       </c>
       <c r="U2" t="n">
-        <v>0.17</v>
+        <v>0.044</v>
       </c>
       <c r="V2" t="n">
         <v>0.001</v>
@@ -1302,68 +1366,68 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>u2net+dino</t>
+          <t>dino448</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.92</v>
+        <v>0.9199199199199199</v>
       </c>
       <c r="C3" t="n">
-        <v>0.917</v>
+        <v>0.907</v>
       </c>
       <c r="D3" t="n">
-        <v>0.918</v>
+        <v>0.889</v>
       </c>
       <c r="E3" t="n">
-        <v>0.914</v>
+        <v>0.885</v>
       </c>
       <c r="F3" t="n">
-        <v>0.906</v>
+        <v>0.881</v>
       </c>
       <c r="G3" t="n">
-        <v>0.898</v>
+        <v>0.859</v>
       </c>
       <c r="H3" t="n">
-        <v>0.902</v>
+        <v>0.839</v>
       </c>
       <c r="I3" t="n">
-        <v>0.891</v>
+        <v>0.824</v>
       </c>
       <c r="J3" t="n">
-        <v>0.887</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.877</v>
+        <v>0.805</v>
       </c>
       <c r="L3" t="n">
-        <v>0.859</v>
+        <v>0.783</v>
       </c>
       <c r="M3" t="n">
-        <v>0.848</v>
+        <v>0.763</v>
       </c>
       <c r="N3" t="n">
-        <v>0.83</v>
+        <v>0.729</v>
       </c>
       <c r="O3" t="n">
-        <v>0.793</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>0.767</v>
+        <v>0.633</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.717</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>0.661</v>
+        <v>0.472</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.371</v>
       </c>
       <c r="T3" t="n">
-        <v>0.417</v>
+        <v>0.234</v>
       </c>
       <c r="U3" t="n">
-        <v>0.206</v>
+        <v>0.09</v>
       </c>
       <c r="V3" t="n">
         <v>0.001</v>
@@ -1372,68 +1436,68 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>u2net+dino_320</t>
+          <t>u2net+dino</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.92</v>
+        <v>0.9199199199199199</v>
       </c>
       <c r="C4" t="n">
-        <v>0.917</v>
+        <v>0.896</v>
       </c>
       <c r="D4" t="n">
-        <v>0.922</v>
+        <v>0.889</v>
       </c>
       <c r="E4" t="n">
-        <v>0.914</v>
+        <v>0.876</v>
       </c>
       <c r="F4" t="n">
-        <v>0.903</v>
+        <v>0.864</v>
       </c>
       <c r="G4" t="n">
-        <v>0.901</v>
+        <v>0.847</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9</v>
+        <v>0.836</v>
       </c>
       <c r="I4" t="n">
-        <v>0.893</v>
+        <v>0.831</v>
       </c>
       <c r="J4" t="n">
-        <v>0.892</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.872</v>
+        <v>0.788</v>
       </c>
       <c r="L4" t="n">
-        <v>0.86</v>
+        <v>0.776</v>
       </c>
       <c r="M4" t="n">
-        <v>0.844</v>
+        <v>0.756</v>
       </c>
       <c r="N4" t="n">
-        <v>0.824</v>
+        <v>0.724</v>
       </c>
       <c r="O4" t="n">
-        <v>0.796</v>
+        <v>0.667</v>
       </c>
       <c r="P4" t="n">
-        <v>0.764</v>
+        <v>0.631</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.721</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>0.665</v>
+        <v>0.493</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.367</v>
       </c>
       <c r="T4" t="n">
-        <v>0.423</v>
+        <v>0.231</v>
       </c>
       <c r="U4" t="n">
-        <v>0.219</v>
+        <v>0.092</v>
       </c>
       <c r="V4" t="n">
         <v>0.001</v>
@@ -1442,68 +1506,68 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dino+u2net_sum</t>
+          <t>dino</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.92</v>
+        <v>0.9199199199199199</v>
       </c>
       <c r="C5" t="n">
-        <v>0.917</v>
+        <v>0.91</v>
       </c>
       <c r="D5" t="n">
-        <v>0.918</v>
+        <v>0.892</v>
       </c>
       <c r="E5" t="n">
-        <v>0.914</v>
+        <v>0.891</v>
       </c>
       <c r="F5" t="n">
-        <v>0.906</v>
+        <v>0.88</v>
       </c>
       <c r="G5" t="n">
-        <v>0.898</v>
+        <v>0.851</v>
       </c>
       <c r="H5" t="n">
-        <v>0.902</v>
+        <v>0.842</v>
       </c>
       <c r="I5" t="n">
-        <v>0.892</v>
+        <v>0.821</v>
       </c>
       <c r="J5" t="n">
-        <v>0.888</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.878</v>
+        <v>0.805</v>
       </c>
       <c r="L5" t="n">
-        <v>0.859</v>
+        <v>0.784</v>
       </c>
       <c r="M5" t="n">
-        <v>0.851</v>
+        <v>0.763</v>
       </c>
       <c r="N5" t="n">
-        <v>0.839</v>
+        <v>0.741</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.698</v>
       </c>
       <c r="P5" t="n">
-        <v>0.776</v>
+        <v>0.637</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.736</v>
+        <v>0.571</v>
       </c>
       <c r="R5" t="n">
-        <v>0.659</v>
+        <v>0.492</v>
       </c>
       <c r="S5" t="n">
-        <v>0.509</v>
+        <v>0.376</v>
       </c>
       <c r="T5" t="n">
-        <v>0.354</v>
+        <v>0.237</v>
       </c>
       <c r="U5" t="n">
-        <v>0.117</v>
+        <v>0.089</v>
       </c>
       <c r="V5" t="n">
         <v>0.001</v>
@@ -1512,68 +1576,68 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dino448</t>
+          <t>u2net</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.92</v>
+        <v>0.9199199199199199</v>
       </c>
       <c r="C6" t="n">
-        <v>0.919</v>
+        <v>0.906</v>
       </c>
       <c r="D6" t="n">
-        <v>0.92</v>
+        <v>0.897</v>
       </c>
       <c r="E6" t="n">
-        <v>0.909</v>
+        <v>0.891</v>
       </c>
       <c r="F6" t="n">
-        <v>0.912</v>
+        <v>0.879</v>
       </c>
       <c r="G6" t="n">
-        <v>0.906</v>
+        <v>0.868</v>
       </c>
       <c r="H6" t="n">
-        <v>0.909</v>
+        <v>0.856</v>
       </c>
       <c r="I6" t="n">
-        <v>0.906</v>
+        <v>0.842</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="K6" t="n">
-        <v>0.897</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>0.882</v>
+        <v>0.795</v>
       </c>
       <c r="M6" t="n">
-        <v>0.868</v>
+        <v>0.766</v>
       </c>
       <c r="N6" t="n">
-        <v>0.854</v>
+        <v>0.735</v>
       </c>
       <c r="O6" t="n">
-        <v>0.832</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>0.793</v>
+        <v>0.642</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.755</v>
+        <v>0.574</v>
       </c>
       <c r="R6" t="n">
-        <v>0.702</v>
+        <v>0.483</v>
       </c>
       <c r="S6" t="n">
-        <v>0.602</v>
+        <v>0.375</v>
       </c>
       <c r="T6" t="n">
-        <v>0.465</v>
+        <v>0.229</v>
       </c>
       <c r="U6" t="n">
-        <v>0.248</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>0.001</v>
@@ -1582,68 +1646,68 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dino448+u2net</t>
+          <t>u2net+dino_320</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.92</v>
+        <v>0.9199199199199199</v>
       </c>
       <c r="C7" t="n">
-        <v>0.92</v>
+        <v>0.898</v>
       </c>
       <c r="D7" t="n">
-        <v>0.918</v>
+        <v>0.886</v>
       </c>
       <c r="E7" t="n">
-        <v>0.916</v>
+        <v>0.873</v>
       </c>
       <c r="F7" t="n">
-        <v>0.917</v>
+        <v>0.871</v>
       </c>
       <c r="G7" t="n">
-        <v>0.914</v>
+        <v>0.847</v>
       </c>
       <c r="H7" t="n">
-        <v>0.908</v>
+        <v>0.831</v>
       </c>
       <c r="I7" t="n">
-        <v>0.909</v>
+        <v>0.834</v>
       </c>
       <c r="J7" t="n">
-        <v>0.899</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.898</v>
+        <v>0.787</v>
       </c>
       <c r="L7" t="n">
-        <v>0.892</v>
+        <v>0.775</v>
       </c>
       <c r="M7" t="n">
-        <v>0.879</v>
+        <v>0.744</v>
       </c>
       <c r="N7" t="n">
-        <v>0.848</v>
+        <v>0.716</v>
       </c>
       <c r="O7" t="n">
-        <v>0.83</v>
+        <v>0.669</v>
       </c>
       <c r="P7" t="n">
-        <v>0.797</v>
+        <v>0.621</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.759</v>
+        <v>0.575</v>
       </c>
       <c r="R7" t="n">
-        <v>0.711</v>
+        <v>0.485</v>
       </c>
       <c r="S7" t="n">
-        <v>0.623</v>
+        <v>0.365</v>
       </c>
       <c r="T7" t="n">
-        <v>0.494</v>
+        <v>0.229</v>
       </c>
       <c r="U7" t="n">
-        <v>0.285</v>
+        <v>0.093</v>
       </c>
       <c r="V7" t="n">
         <v>0.001</v>
@@ -1652,75 +1716,145 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>dino448+u2net</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.9199199199199199</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.894</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.856</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.734</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>dinov2_COMBO_ENT_SMOOTH</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.919</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.923</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.919</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.912</v>
-      </c>
-      <c r="H8" t="n">
+      <c r="B9" t="n">
+        <v>0.9199199199199199</v>
+      </c>
+      <c r="C9" t="n">
         <v>0.914</v>
       </c>
-      <c r="I8" t="n">
-        <v>0.908</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.892</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.888</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.886</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.856</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.838</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.783</v>
-      </c>
-      <c r="R8" t="n">
+      <c r="D9" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.898</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.863</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="O9" t="n">
         <v>0.751</v>
       </c>
-      <c r="S8" t="n">
-        <v>0.6909999999999999</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="P9" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="V9" t="n">
         <v>0.001</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:V8">
+  <conditionalFormatting sqref="B2:V9">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -1743,11 +1877,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
@@ -1843,68 +1977,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>u2net</t>
+          <t>dino+u2net_sum</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.99</v>
+        <v>0.9869869869869869</v>
       </c>
       <c r="C2" t="n">
-        <v>0.988</v>
+        <v>0.979</v>
       </c>
       <c r="D2" t="n">
-        <v>0.987</v>
+        <v>0.976</v>
       </c>
       <c r="E2" t="n">
-        <v>0.985</v>
+        <v>0.97</v>
       </c>
       <c r="F2" t="n">
-        <v>0.983</v>
+        <v>0.967</v>
       </c>
       <c r="G2" t="n">
-        <v>0.983</v>
+        <v>0.956</v>
       </c>
       <c r="H2" t="n">
-        <v>0.979</v>
+        <v>0.951</v>
       </c>
       <c r="I2" t="n">
-        <v>0.976</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>0.975</v>
+        <v>0.93</v>
       </c>
       <c r="K2" t="n">
-        <v>0.972</v>
+        <v>0.912</v>
       </c>
       <c r="L2" t="n">
-        <v>0.964</v>
+        <v>0.888</v>
       </c>
       <c r="M2" t="n">
-        <v>0.956</v>
+        <v>0.848</v>
       </c>
       <c r="N2" t="n">
-        <v>0.945</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>0.929</v>
+        <v>0.748</v>
       </c>
       <c r="P2" t="n">
-        <v>0.904</v>
+        <v>0.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.872</v>
+        <v>0.575</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.459</v>
       </c>
       <c r="S2" t="n">
-        <v>0.713</v>
+        <v>0.352</v>
       </c>
       <c r="T2" t="n">
-        <v>0.553</v>
+        <v>0.223</v>
       </c>
       <c r="U2" t="n">
-        <v>0.291</v>
+        <v>0.098</v>
       </c>
       <c r="V2" t="n">
         <v>0.005</v>
@@ -1913,68 +2047,68 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>u2net+dino_320</t>
+          <t>u2net+dino</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.99</v>
+        <v>0.9869869869869869</v>
       </c>
       <c r="C3" t="n">
-        <v>0.988</v>
+        <v>0.979</v>
       </c>
       <c r="D3" t="n">
-        <v>0.986</v>
+        <v>0.976</v>
       </c>
       <c r="E3" t="n">
-        <v>0.983</v>
+        <v>0.97</v>
       </c>
       <c r="F3" t="n">
-        <v>0.984</v>
+        <v>0.968</v>
       </c>
       <c r="G3" t="n">
-        <v>0.983</v>
+        <v>0.958</v>
       </c>
       <c r="H3" t="n">
-        <v>0.983</v>
+        <v>0.955</v>
       </c>
       <c r="I3" t="n">
-        <v>0.98</v>
+        <v>0.949</v>
       </c>
       <c r="J3" t="n">
-        <v>0.979</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.978</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>0.977</v>
+        <v>0.925</v>
       </c>
       <c r="M3" t="n">
-        <v>0.962</v>
+        <v>0.909</v>
       </c>
       <c r="N3" t="n">
-        <v>0.959</v>
+        <v>0.893</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.855</v>
       </c>
       <c r="P3" t="n">
-        <v>0.911</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.878</v>
+        <v>0.748</v>
       </c>
       <c r="R3" t="n">
-        <v>0.834</v>
+        <v>0.679</v>
       </c>
       <c r="S3" t="n">
-        <v>0.76</v>
+        <v>0.575</v>
       </c>
       <c r="T3" t="n">
-        <v>0.609</v>
+        <v>0.392</v>
       </c>
       <c r="U3" t="n">
-        <v>0.359</v>
+        <v>0.188</v>
       </c>
       <c r="V3" t="n">
         <v>0.005</v>
@@ -1983,68 +2117,68 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>u2net+dino</t>
+          <t>u2net+dino_320</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.99</v>
+        <v>0.9869869869869869</v>
       </c>
       <c r="C4" t="n">
-        <v>0.987</v>
+        <v>0.978</v>
       </c>
       <c r="D4" t="n">
-        <v>0.985</v>
+        <v>0.976</v>
       </c>
       <c r="E4" t="n">
-        <v>0.984</v>
+        <v>0.972</v>
       </c>
       <c r="F4" t="n">
-        <v>0.985</v>
+        <v>0.968</v>
       </c>
       <c r="G4" t="n">
-        <v>0.982</v>
+        <v>0.959</v>
       </c>
       <c r="H4" t="n">
-        <v>0.984</v>
+        <v>0.955</v>
       </c>
       <c r="I4" t="n">
-        <v>0.98</v>
+        <v>0.948</v>
       </c>
       <c r="J4" t="n">
-        <v>0.977</v>
+        <v>0.945</v>
       </c>
       <c r="K4" t="n">
-        <v>0.977</v>
+        <v>0.927</v>
       </c>
       <c r="L4" t="n">
-        <v>0.975</v>
+        <v>0.923</v>
       </c>
       <c r="M4" t="n">
-        <v>0.961</v>
+        <v>0.908</v>
       </c>
       <c r="N4" t="n">
-        <v>0.954</v>
+        <v>0.892</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.856</v>
       </c>
       <c r="P4" t="n">
-        <v>0.915</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.88</v>
+        <v>0.752</v>
       </c>
       <c r="R4" t="n">
-        <v>0.836</v>
+        <v>0.681</v>
       </c>
       <c r="S4" t="n">
-        <v>0.766</v>
+        <v>0.577</v>
       </c>
       <c r="T4" t="n">
-        <v>0.616</v>
+        <v>0.387</v>
       </c>
       <c r="U4" t="n">
-        <v>0.362</v>
+        <v>0.19</v>
       </c>
       <c r="V4" t="n">
         <v>0.005</v>
@@ -2053,68 +2187,68 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dino+u2net_sum</t>
+          <t>dino</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.99</v>
+        <v>0.9869869869869869</v>
       </c>
       <c r="C5" t="n">
         <v>0.987</v>
       </c>
       <c r="D5" t="n">
-        <v>0.985</v>
+        <v>0.981</v>
       </c>
       <c r="E5" t="n">
-        <v>0.984</v>
+        <v>0.983</v>
       </c>
       <c r="F5" t="n">
-        <v>0.985</v>
+        <v>0.973</v>
       </c>
       <c r="G5" t="n">
-        <v>0.982</v>
+        <v>0.969</v>
       </c>
       <c r="H5" t="n">
-        <v>0.984</v>
+        <v>0.963</v>
       </c>
       <c r="I5" t="n">
-        <v>0.979</v>
+        <v>0.952</v>
       </c>
       <c r="J5" t="n">
-        <v>0.975</v>
+        <v>0.949</v>
       </c>
       <c r="K5" t="n">
-        <v>0.976</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.974</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.96</v>
+        <v>0.918</v>
       </c>
       <c r="N5" t="n">
-        <v>0.952</v>
+        <v>0.896</v>
       </c>
       <c r="O5" t="n">
-        <v>0.945</v>
+        <v>0.866</v>
       </c>
       <c r="P5" t="n">
-        <v>0.928</v>
+        <v>0.821</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.892</v>
+        <v>0.763</v>
       </c>
       <c r="R5" t="n">
-        <v>0.84</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>0.727</v>
+        <v>0.576</v>
       </c>
       <c r="T5" t="n">
-        <v>0.547</v>
+        <v>0.423</v>
       </c>
       <c r="U5" t="n">
-        <v>0.227</v>
+        <v>0.193</v>
       </c>
       <c r="V5" t="n">
         <v>0.005</v>
@@ -2127,64 +2261,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.99</v>
+        <v>0.9869869869869869</v>
       </c>
       <c r="C6" t="n">
-        <v>0.986</v>
+        <v>0.987</v>
       </c>
       <c r="D6" t="n">
-        <v>0.986</v>
+        <v>0.981</v>
       </c>
       <c r="E6" t="n">
-        <v>0.985</v>
+        <v>0.981</v>
       </c>
       <c r="F6" t="n">
-        <v>0.985</v>
+        <v>0.976</v>
       </c>
       <c r="G6" t="n">
-        <v>0.984</v>
+        <v>0.971</v>
       </c>
       <c r="H6" t="n">
-        <v>0.982</v>
+        <v>0.958</v>
       </c>
       <c r="I6" t="n">
-        <v>0.983</v>
+        <v>0.953</v>
       </c>
       <c r="J6" t="n">
-        <v>0.981</v>
+        <v>0.945</v>
       </c>
       <c r="K6" t="n">
-        <v>0.978</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>0.977</v>
+        <v>0.928</v>
       </c>
       <c r="M6" t="n">
-        <v>0.972</v>
+        <v>0.918</v>
       </c>
       <c r="N6" t="n">
-        <v>0.966</v>
+        <v>0.899</v>
       </c>
       <c r="O6" t="n">
-        <v>0.96</v>
+        <v>0.863</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.819</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.907</v>
+        <v>0.763</v>
       </c>
       <c r="R6" t="n">
-        <v>0.873</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>0.799</v>
+        <v>0.57</v>
       </c>
       <c r="T6" t="n">
-        <v>0.674</v>
+        <v>0.413</v>
       </c>
       <c r="U6" t="n">
-        <v>0.393</v>
+        <v>0.185</v>
       </c>
       <c r="V6" t="n">
         <v>0.005</v>
@@ -2193,68 +2327,68 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dino448+u2net</t>
+          <t>u2net</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.99</v>
+        <v>0.9869869869869869</v>
       </c>
       <c r="C7" t="n">
-        <v>0.988</v>
+        <v>0.985</v>
       </c>
       <c r="D7" t="n">
-        <v>0.987</v>
+        <v>0.98</v>
       </c>
       <c r="E7" t="n">
-        <v>0.985</v>
+        <v>0.975</v>
       </c>
       <c r="F7" t="n">
-        <v>0.985</v>
+        <v>0.972</v>
       </c>
       <c r="G7" t="n">
-        <v>0.984</v>
+        <v>0.967</v>
       </c>
       <c r="H7" t="n">
-        <v>0.983</v>
+        <v>0.959</v>
       </c>
       <c r="I7" t="n">
-        <v>0.982</v>
+        <v>0.955</v>
       </c>
       <c r="J7" t="n">
-        <v>0.985</v>
+        <v>0.95</v>
       </c>
       <c r="K7" t="n">
-        <v>0.983</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>0.979</v>
+        <v>0.92</v>
       </c>
       <c r="M7" t="n">
-        <v>0.973</v>
+        <v>0.909</v>
       </c>
       <c r="N7" t="n">
-        <v>0.966</v>
+        <v>0.89</v>
       </c>
       <c r="O7" t="n">
-        <v>0.958</v>
+        <v>0.876</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.823</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.914</v>
+        <v>0.765</v>
       </c>
       <c r="R7" t="n">
-        <v>0.869</v>
+        <v>0.667</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.549</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="U7" t="n">
-        <v>0.44</v>
+        <v>0.164</v>
       </c>
       <c r="V7" t="n">
         <v>0.005</v>
@@ -2263,75 +2397,145 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>dino448+u2net</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.9869869869869869</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.898</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>dinov2_COMBO_ENT_SMOOTH</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.989</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="B9" t="n">
+        <v>0.9869869869869869</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="D9" t="n">
         <v>0.985</v>
       </c>
-      <c r="E8" t="n">
-        <v>0.984</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.988</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.986</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.983</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.978</v>
-      </c>
-      <c r="J8" t="n">
+      <c r="E9" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="G9" t="n">
         <v>0.981</v>
       </c>
-      <c r="K8" t="n">
+      <c r="H9" t="n">
         <v>0.975</v>
       </c>
-      <c r="L8" t="n">
-        <v>0.972</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.969</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="I9" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="J9" t="n">
         <v>0.964</v>
       </c>
-      <c r="O8" t="n">
-        <v>0.954</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.9389999999999999</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.927</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.902</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.849</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.759</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="K9" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="V9" t="n">
         <v>0.005</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:V8">
+  <conditionalFormatting sqref="B2:V9">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
